--- a/tools/keybind_sheet/MidnightHelper_Keybinds.xlsx
+++ b/tools/keybind_sheet/MidnightHelper_Keybinds.xlsx
@@ -4571,7 +4571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4893,7 +4893,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Arcane Explosion</t>
+          <t>Supernova</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
@@ -4910,7 +4910,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Supernova</t>
+          <t>Arcane Explosion</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
@@ -5038,15 +5038,49 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+R</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Slow Fall</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+    </row>
     <row r="29">
-      <c r="A29" s="18" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+V</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Spellsteal</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="18" t="inlineStr">
         <is>
           <t>Situational (no fixed key — bind where you like):</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Mirror Image, Spellsteal</t>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Dragon's Breath, Mirror Image</t>
         </is>
       </c>
     </row>
@@ -5061,7 +5095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5395,80 +5429,80 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Shift+4</t>
+          <t>Shift+2</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Flamestrike</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>Spender</t>
+          <t>Arcane Explosion</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Rotation</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Shift+F</t>
+          <t>Shift+4</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Invisibility</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>Utility</t>
+          <t>Flamestrike</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>Spender</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Shift+X</t>
+          <t>Shift+F</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Remove Curse</t>
-        </is>
-      </c>
-      <c r="C22" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
+          <t>Invisibility</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Shift+Z</t>
+          <t>Shift+R</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Greater Invisibility</t>
-        </is>
-      </c>
-      <c r="C23" s="14" t="inlineStr">
-        <is>
-          <t>Defensive</t>
+          <t>Slow Fall</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Shift+C</t>
+          <t>Shift+X</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Ring of Frost</t>
+          <t>Remove Curse</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
@@ -5480,29 +5514,29 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Shift+V</t>
+          <t>Shift+Z</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Polymorph</t>
-        </is>
-      </c>
-      <c r="C25" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
+          <t>Greater Invisibility</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>Defensive</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Ctrl+X</t>
+          <t>Shift+C</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Spellsteal</t>
+          <t>Ring of Frost</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
@@ -5514,27 +5548,61 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
+          <t>Shift+V</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Polymorph</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+X</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Spellsteal</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
           <t>Ctrl+V</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>Dragon's Breath</t>
         </is>
       </c>
-      <c r="C27" s="13" t="inlineStr">
+      <c r="C29" s="13" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="18" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="18" t="inlineStr">
         <is>
           <t>Situational (no fixed key — bind where you like):</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Cauterize, Mirror Image</t>
         </is>
@@ -5551,7 +5619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5936,63 +6004,63 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Shift+F</t>
+          <t>Shift+5</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Invisibility</t>
-        </is>
-      </c>
-      <c r="C23" s="12" t="inlineStr">
-        <is>
-          <t>Utility</t>
+          <t>Arcane Explosion</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>Rotation</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Shift+X</t>
+          <t>Shift+F</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Remove Curse</t>
-        </is>
-      </c>
-      <c r="C24" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
+          <t>Invisibility</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Shift+Z</t>
+          <t>Shift+R</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Greater Invisibility</t>
-        </is>
-      </c>
-      <c r="C25" s="14" t="inlineStr">
-        <is>
-          <t>Defensive</t>
+          <t>Slow Fall</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Shift+C</t>
+          <t>Shift+X</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Ring of Frost</t>
+          <t>Remove Curse</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
@@ -6004,29 +6072,80 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
+          <t>Shift+Z</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Greater Invisibility</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>Defensive</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Shift+C</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Ring of Frost</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
           <t>Shift+V</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>Polymorph</t>
         </is>
       </c>
-      <c r="C27" s="13" t="inlineStr">
+      <c r="C29" s="13" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="18" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+V</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Spellsteal</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="18" t="inlineStr">
         <is>
           <t>Situational (no fixed key — bind where you like):</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Mirror Image, Spellsteal</t>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Dragon's Breath, Mirror Image</t>
         </is>
       </c>
     </row>

--- a/tools/keybind_sheet/MidnightHelper_Keybinds.xlsx
+++ b/tools/keybind_sheet/MidnightHelper_Keybinds.xlsx
@@ -5063,7 +5063,7 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Spellsteal</t>
+          <t>Dragon's Breath</t>
         </is>
       </c>
       <c r="C29" s="13" t="inlineStr">
@@ -5080,7 +5080,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Dragon's Breath, Mirror Image</t>
+          <t>Mirror Image, Spellsteal</t>
         </is>
       </c>
     </row>
@@ -5565,17 +5565,17 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Ctrl+X</t>
+          <t>Ctrl+Z</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Spellsteal</t>
-        </is>
-      </c>
-      <c r="C28" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
+          <t>Mirror Image</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="inlineStr">
+        <is>
+          <t>Defensive</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Cauterize, Mirror Image</t>
+          <t>Cauterize, Spellsteal</t>
         </is>
       </c>
     </row>
@@ -6128,7 +6128,7 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Spellsteal</t>
+          <t>Dragon's Breath</t>
         </is>
       </c>
       <c r="C30" s="13" t="inlineStr">
@@ -6145,7 +6145,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Dragon's Breath, Mirror Image</t>
+          <t>Mirror Image, Spellsteal</t>
         </is>
       </c>
     </row>

--- a/tools/keybind_sheet/MidnightHelper_Keybinds.xlsx
+++ b/tools/keybind_sheet/MidnightHelper_Keybinds.xlsx
@@ -852,7 +852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1319,25 +1319,59 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+F</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Prowl</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+    </row>
     <row r="29">
-      <c r="A29" s="18" t="inlineStr">
-        <is>
-          <t>Situational (no fixed key — bind where you like):</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Bear Form, Prowl, Soothe</t>
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+V</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Soothe</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="18" t="inlineStr">
         <is>
+          <t>Situational (no fixed key — bind where you like):</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Bear Form</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="18" t="inlineStr">
+        <is>
           <t>Click-cast / mouseover (raid frames, not keys):</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Cenarion Ward, Lifebloom, Regrowth, Rejuvenation, Swiftmend</t>
         </is>
@@ -2293,7 +2327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2700,7 +2734,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Time Dilation</t>
+          <t>Rewind</t>
         </is>
       </c>
       <c r="C24" s="15" t="inlineStr">
@@ -2712,39 +2746,44 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
+          <t>Ctrl+F2</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Time Dilation</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>Cooldown</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
           <t>Ctrl+F3</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Tip the Scales</t>
-        </is>
-      </c>
-      <c r="C25" s="15" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Fury of the Aspects</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="inlineStr">
         <is>
           <t>Cooldown</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="18" t="inlineStr">
-        <is>
-          <t>Situational (no fixed key — bind where you like):</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Fury of the Aspects, Rewind</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="18" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="18" t="inlineStr">
         <is>
           <t>Click-cast / mouseover (raid frames, not keys):</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Echo, Reversion, Spiritbloom</t>
         </is>
@@ -2756,6 +2795,586 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Ability</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>Counter Shot</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>Interrupt</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Disengage</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Steady Shot</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Rotation</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Kill Command</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Rotation</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Barbed Shot</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Rotation</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Cobra Shot</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Rotation</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Kill Shot</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>Spender</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Mend Pet</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Hunter's Mark</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Roar of Sacrifice</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>Defensive</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Survival of the Fittest</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>Defensive</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Aspect of the Turtle</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>Defensive (major)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Tranquilizing Shot</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Bestial Wrath</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>Big cooldown</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Exhilaration</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>Self-heal</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Call of the Wild</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>Cooldown</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Recuperate</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>Sustain / HoT</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Shift+Q</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Aspect of the Cheetah</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Shift+1</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Multi-Shot</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Rotation</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Shift+F</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Misdirection</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Shift+R</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Feign Death</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Shift+X</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Binding Shot</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Shift+C</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Intimidation</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Shift+V</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Freezing Trap</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Shift+F1</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Bloodshed</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>Cooldown</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Shift+F2</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Primal Rage</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>Cooldown</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Shift+F3</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Stampede</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="inlineStr">
+        <is>
+          <t>Cooldown</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+F</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Camouflage</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+R</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Flare</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+X</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Concussive Shot</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+C</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Bursting Shot</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+V</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Scatter Shot</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2845,7 +3464,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Kill Command</t>
+          <t>Aimed Shot</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
@@ -2862,7 +3481,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Barbed Shot</t>
+          <t>Rapid Fire</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
@@ -2879,12 +3498,12 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Cobra Shot</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>Rotation</t>
+          <t>Arcane Shot</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>Spender</t>
         </is>
       </c>
     </row>
@@ -2896,7 +3515,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Kill Shot</t>
+          <t>Black Arrow</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
@@ -3015,7 +3634,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Bestial Wrath</t>
+          <t>Trueshot</t>
         </is>
       </c>
       <c r="C15" s="15" t="inlineStr">
@@ -3049,7 +3668,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Call of the Wild</t>
+          <t>Stampede</t>
         </is>
       </c>
       <c r="C17" s="15" t="inlineStr">
@@ -3112,808 +3731,216 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Shift+F</t>
+          <t>Shift+2</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Misdirection</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>Utility</t>
+          <t>Volley</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>Rotation</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Shift+R</t>
+          <t>Shift+3</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Feign Death</t>
-        </is>
-      </c>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>Utility</t>
+          <t>Wailing Arrow</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>Rotation</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Shift+X</t>
+          <t>Shift+4</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Binding Shot</t>
-        </is>
-      </c>
-      <c r="C23" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
+          <t>Explosive Shot</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>Rotation</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Shift+C</t>
+          <t>Shift+5</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Intimidation</t>
-        </is>
-      </c>
-      <c r="C24" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
+          <t>Chimaera Shot</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Rotation</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Shift+V</t>
+          <t>Shift+F</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Freezing Trap</t>
-        </is>
-      </c>
-      <c r="C25" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
+          <t>Misdirection</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Shift+F1</t>
+          <t>Shift+R</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Bloodshed</t>
-        </is>
-      </c>
-      <c r="C26" s="15" t="inlineStr">
-        <is>
-          <t>Cooldown</t>
+          <t>Feign Death</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Shift+F2</t>
+          <t>Shift+X</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Primal Rage</t>
-        </is>
-      </c>
-      <c r="C27" s="15" t="inlineStr">
-        <is>
-          <t>Cooldown</t>
+          <t>Binding Shot</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Shift+F3</t>
+          <t>Shift+C</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Stampede</t>
-        </is>
-      </c>
-      <c r="C28" s="15" t="inlineStr">
-        <is>
-          <t>Cooldown</t>
+          <t>Intimidation</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Ctrl+F</t>
+          <t>Shift+V</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Camouflage</t>
-        </is>
-      </c>
-      <c r="C29" s="12" t="inlineStr">
-        <is>
-          <t>Utility</t>
+          <t>Freezing Trap</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Ctrl+R</t>
+          <t>Ctrl+4</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Flare</t>
-        </is>
-      </c>
-      <c r="C30" s="12" t="inlineStr">
-        <is>
-          <t>Utility</t>
+          <t>Kill Shot</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>Spender</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Ctrl+X</t>
+          <t>Ctrl+F</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Wyvern Sting</t>
-        </is>
-      </c>
-      <c r="C31" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
+          <t>Camouflage</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>Ctrl+C</t>
+          <t>Ctrl+R</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>Scare Beast</t>
-        </is>
-      </c>
-      <c r="C32" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
+          <t>Flare</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>Ctrl+V</t>
+          <t>Ctrl+X</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Bursting Shot</t>
-        </is>
-      </c>
-      <c r="C33" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="18" t="inlineStr">
-        <is>
-          <t>Situational (no fixed key — bind where you like):</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Concussive Shot, Scatter Shot</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C37"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>Key</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>Ability</t>
-        </is>
-      </c>
-      <c r="C1" s="5" t="inlineStr">
-        <is>
-          <t>Role</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>Counter Shot</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>Interrupt</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>Q</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>Disengage</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>Movement</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Steady Shot</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>Rotation</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Aimed Shot</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>Rotation</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Rapid Fire</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>Rotation</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>Arcane Shot</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>Spender</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Black Arrow</t>
-        </is>
-      </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>Spender</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Mend Pet</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>Utility</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Hunter's Mark</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>Utility</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Roar of Sacrifice</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>Defensive</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Survival of the Fittest</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>Defensive</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Aspect of the Turtle</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="inlineStr">
-        <is>
-          <t>Defensive (major)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Tranquilizing Shot</t>
-        </is>
-      </c>
-      <c r="C14" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>F1</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Trueshot</t>
-        </is>
-      </c>
-      <c r="C15" s="15" t="inlineStr">
-        <is>
-          <t>Big cooldown</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>F2</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Exhilaration</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>Self-heal</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>F3</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Stampede</t>
-        </is>
-      </c>
-      <c r="C17" s="15" t="inlineStr">
-        <is>
-          <t>Cooldown</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>F4</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Recuperate</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>Sustain / HoT</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>Shift+Q</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Aspect of the Cheetah</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>Movement</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>Shift+1</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Multi-Shot</t>
-        </is>
-      </c>
-      <c r="C20" s="10" t="inlineStr">
-        <is>
-          <t>Rotation</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>Shift+2</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Volley</t>
-        </is>
-      </c>
-      <c r="C21" s="10" t="inlineStr">
-        <is>
-          <t>Rotation</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>Shift+3</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Wailing Arrow</t>
-        </is>
-      </c>
-      <c r="C22" s="10" t="inlineStr">
-        <is>
-          <t>Rotation</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>Shift+4</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Explosive Shot</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="inlineStr">
-        <is>
-          <t>Rotation</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>Shift+5</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Chimaera Shot</t>
-        </is>
-      </c>
-      <c r="C24" s="10" t="inlineStr">
-        <is>
-          <t>Rotation</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>Shift+F</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Misdirection</t>
-        </is>
-      </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>Utility</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>Shift+R</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Feign Death</t>
-        </is>
-      </c>
-      <c r="C26" s="12" t="inlineStr">
-        <is>
-          <t>Utility</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>Shift+X</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>Binding Shot</t>
-        </is>
-      </c>
-      <c r="C27" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Shift+C</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>Intimidation</t>
-        </is>
-      </c>
-      <c r="C28" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>Shift+V</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>Freezing Trap</t>
-        </is>
-      </c>
-      <c r="C29" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>Ctrl+4</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>Kill Shot</t>
-        </is>
-      </c>
-      <c r="C30" s="11" t="inlineStr">
-        <is>
-          <t>Spender</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>Ctrl+F</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>Camouflage</t>
-        </is>
-      </c>
-      <c r="C31" s="12" t="inlineStr">
-        <is>
-          <t>Utility</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>Ctrl+R</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>Flare</t>
-        </is>
-      </c>
-      <c r="C32" s="12" t="inlineStr">
-        <is>
-          <t>Utility</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>Ctrl+X</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>Wyvern Sting</t>
+          <t>Concussive Shot</t>
         </is>
       </c>
       <c r="C33" s="13" t="inlineStr">
@@ -3930,7 +3957,7 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>Scare Beast</t>
+          <t>Bursting Shot</t>
         </is>
       </c>
       <c r="C34" s="13" t="inlineStr">
@@ -3947,24 +3974,12 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>Bursting Shot</t>
+          <t>Scatter Shot</t>
         </is>
       </c>
       <c r="C35" s="13" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="18" t="inlineStr">
-        <is>
-          <t>Situational (no fixed key — bind where you like):</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Concussive Shot, Scatter Shot</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4471,7 +4486,7 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Camouflage</t>
+          <t>Feign Death</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
@@ -4488,7 +4503,7 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Flare</t>
+          <t>Camouflage</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
@@ -4505,7 +4520,7 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Bursting Shot</t>
+          <t>Concussive Shot</t>
         </is>
       </c>
       <c r="C31" s="13" t="inlineStr">
@@ -4522,7 +4537,7 @@
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>Wyvern Sting</t>
+          <t>Bursting Shot</t>
         </is>
       </c>
       <c r="C32" s="13" t="inlineStr">
@@ -4539,24 +4554,12 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Concussive Shot</t>
+          <t>Scatter Shot</t>
         </is>
       </c>
       <c r="C33" s="13" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="18" t="inlineStr">
-        <is>
-          <t>Situational (no fixed key — bind where you like):</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Feign Death, Scatter Shot</t>
         </is>
       </c>
     </row>
@@ -5058,29 +5061,51 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
+          <t>Ctrl+X</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Dragon's Breath</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+Z</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Mirror Image</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>Defensive</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
           <t>Ctrl+V</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>Dragon's Breath</t>
-        </is>
-      </c>
-      <c r="C29" s="13" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Spellsteal</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="18" t="inlineStr">
-        <is>
-          <t>Situational (no fixed key — bind where you like):</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Mirror Image, Spellsteal</t>
         </is>
       </c>
     </row>
@@ -5565,46 +5590,68 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Ctrl+Z</t>
+          <t>Ctrl+X</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Mirror Image</t>
-        </is>
-      </c>
-      <c r="C28" s="14" t="inlineStr">
-        <is>
-          <t>Defensive</t>
+          <t>Dragon's Breath</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
+          <t>Ctrl+Z</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Cauterize</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>Defensive</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+C</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Mirror Image</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>Defensive</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
           <t>Ctrl+V</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>Dragon's Breath</t>
-        </is>
-      </c>
-      <c r="C29" s="13" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Spellsteal</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="18" t="inlineStr">
-        <is>
-          <t>Situational (no fixed key — bind where you like):</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Cauterize, Spellsteal</t>
         </is>
       </c>
     </row>
@@ -6123,29 +6170,51 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
+          <t>Ctrl+X</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Dragon's Breath</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+Z</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Mirror Image</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>Defensive</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
           <t>Ctrl+V</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>Dragon's Breath</t>
-        </is>
-      </c>
-      <c r="C30" s="13" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Spellsteal</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="18" t="inlineStr">
-        <is>
-          <t>Situational (no fixed key — bind where you like):</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Mirror Image, Spellsteal</t>
         </is>
       </c>
     </row>
@@ -6644,15 +6713,37 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+V</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Strangulate</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
+        </is>
+      </c>
+    </row>
     <row r="30">
-      <c r="A30" s="18" t="inlineStr">
-        <is>
-          <t>Situational (no fixed key — bind where you like):</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Empower Rune Weapon, Strangulate</t>
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+F1</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Empower Rune Weapon</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="inlineStr">
+        <is>
+          <t>Cooldown</t>
         </is>
       </c>
     </row>
@@ -7060,7 +7151,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7459,25 +7550,42 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="18" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+F1</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Touch of Death</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>Cooldown</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="18" t="inlineStr">
         <is>
           <t>Situational (no fixed key — bind where you like):</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Thunder Focus Tea, Touch of Death</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="18" t="inlineStr">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Thunder Focus Tea</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="18" t="inlineStr">
         <is>
           <t>Click-cast / mouseover (raid frames, not keys):</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Enveloping Mist, Renewing Mist, Sheilun's Gift, Soothing Mist</t>
         </is>
@@ -7904,7 +8012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8345,7 +8453,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Turn Evil</t>
+          <t>Repentance</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
@@ -8379,7 +8487,7 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Blessing of Freedom</t>
+          <t>Turn Evil</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr">
@@ -8396,7 +8504,7 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Repentance</t>
+          <t>Blinding Light</t>
         </is>
       </c>
       <c r="C29" s="13" t="inlineStr">
@@ -8405,25 +8513,30 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="18" t="inlineStr">
-        <is>
-          <t>Situational (no fixed key — bind where you like):</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Avenging Crusader, Blinding Light</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="18" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+F1</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Avenging Crusader</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="inlineStr">
+        <is>
+          <t>Big cooldown</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="18" t="inlineStr">
         <is>
           <t>Click-cast / mouseover (raid frames, not keys):</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Beacon of Faith, Beacon of Light, Bestow Faith, Flash of Light, Holy Light, Holy Shock</t>
         </is>
@@ -8440,7 +8553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8932,7 +9045,7 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Blessing of Spellwarding</t>
+          <t>Blessing of Protection</t>
         </is>
       </c>
       <c r="C29" s="14" t="inlineStr">
@@ -8949,12 +9062,12 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Turn Evil</t>
-        </is>
-      </c>
-      <c r="C30" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
+          <t>Blessing of Sacrifice</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>Defensive</t>
         </is>
       </c>
     </row>
@@ -8972,18 +9085,6 @@
       <c r="C31" s="13" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="18" t="inlineStr">
-        <is>
-          <t>Situational (no fixed key — bind where you like):</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Blessing of Protection, Blessing of Sacrifice</t>
         </is>
       </c>
     </row>
@@ -8998,7 +9099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9473,7 +9574,7 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Turn Evil</t>
+          <t>Repentance</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr">
@@ -9490,7 +9591,7 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Blessing of Spellwarding</t>
+          <t>Blessing of Sacrifice</t>
         </is>
       </c>
       <c r="C29" s="14" t="inlineStr">
@@ -9507,12 +9608,12 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Blessing of Freedom</t>
-        </is>
-      </c>
-      <c r="C30" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
+          <t>Blessing of Spellwarding</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>Defensive</t>
         </is>
       </c>
     </row>
@@ -9524,24 +9625,12 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Repentance</t>
+          <t>Blinding Light</t>
         </is>
       </c>
       <c r="C31" s="13" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="18" t="inlineStr">
-        <is>
-          <t>Situational (no fixed key — bind where you like):</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Blessing of Sacrifice, Blinding Light</t>
         </is>
       </c>
     </row>
@@ -10007,7 +10096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10423,25 +10512,30 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="18" t="inlineStr">
-        <is>
-          <t>Situational (no fixed key — bind where you like):</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+F</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>Levitate</t>
         </is>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="18" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="18" t="inlineStr">
         <is>
           <t>Click-cast / mouseover (raid frames, not keys):</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Flash Heal, Heal, Holy Word: Serenity, Prayer of Mending, Renew, Shadow Mend</t>
         </is>
@@ -11335,15 +11429,37 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+X</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Gouge</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
+        </is>
+      </c>
+    </row>
     <row r="27">
-      <c r="A27" s="18" t="inlineStr">
-        <is>
-          <t>Situational (no fixed key — bind where you like):</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Gouge, Sap</t>
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+V</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Sap</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
@@ -12286,15 +12402,37 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+X</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Gouge</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
+        </is>
+      </c>
+    </row>
     <row r="28">
-      <c r="A28" s="18" t="inlineStr">
-        <is>
-          <t>Situational (no fixed key — bind where you like):</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Gouge, Sap</t>
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+V</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Sap</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
@@ -12759,15 +12897,37 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+X</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Gouge</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
+        </is>
+      </c>
+    </row>
     <row r="28">
-      <c r="A28" s="18" t="inlineStr">
-        <is>
-          <t>Situational (no fixed key — bind where you like):</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Gouge, Sap</t>
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+V</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Sap</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
@@ -12782,7 +12942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13232,15 +13392,20 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="18" t="inlineStr">
-        <is>
-          <t>Situational (no fixed key — bind where you like):</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+F</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>Nature's Swiftness</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
         </is>
       </c>
     </row>
@@ -13725,29 +13890,51 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
+          <t>Ctrl+Q</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Ghost Wolf</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>Movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
           <t>Ctrl+F1</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Heroism</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="inlineStr">
+        <is>
+          <t>Cooldown</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+F3</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>Primordial Wave</t>
         </is>
       </c>
-      <c r="C28" s="15" t="inlineStr">
+      <c r="C30" s="15" t="inlineStr">
         <is>
           <t>Cooldown</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="18" t="inlineStr">
-        <is>
-          <t>Situational (no fixed key — bind where you like):</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Ghost Wolf, Heroism</t>
         </is>
       </c>
     </row>
@@ -13762,7 +13949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14178,25 +14365,30 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="18" t="inlineStr">
-        <is>
-          <t>Situational (no fixed key — bind where you like):</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+F</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>Nature's Swiftness</t>
         </is>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="18" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="18" t="inlineStr">
         <is>
           <t>Click-cast / mouseover (raid frames, not keys):</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Healing Wave, Riptide, Unleash Life</t>
         </is>
@@ -14748,15 +14940,37 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+F</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Create Soulwell</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+    </row>
     <row r="33">
-      <c r="A33" s="18" t="inlineStr">
-        <is>
-          <t>Situational (no fixed key — bind where you like):</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Create Soulwell, Vile Taint</t>
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+F1</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Vile Taint</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="inlineStr">
+        <is>
+          <t>Cooldown</t>
         </is>
       </c>
     </row>
@@ -14771,7 +14985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15221,15 +15435,20 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="18" t="inlineStr">
-        <is>
-          <t>Situational (no fixed key — bind where you like):</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+F</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>Create Soulwell</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
         </is>
       </c>
     </row>
@@ -15745,15 +15964,37 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+F</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Create Soulwell</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+    </row>
     <row r="31">
-      <c r="A31" s="18" t="inlineStr">
-        <is>
-          <t>Situational (no fixed key — bind where you like):</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Create Soulwell, Havoc</t>
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+R</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Havoc</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
         </is>
       </c>
     </row>
@@ -15768,7 +16009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16286,15 +16527,20 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="18" t="inlineStr">
-        <is>
-          <t>Situational (no fixed key — bind where you like):</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+F1</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>Demolish</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="inlineStr">
+        <is>
+          <t>Cooldown</t>
         </is>
       </c>
     </row>
@@ -17299,7 +17545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17825,7 +18071,7 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Shattering Throw</t>
+          <t>Wrecking Throw</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
@@ -17842,7 +18088,7 @@
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>Challenging Shout</t>
+          <t>Shattering Throw</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
@@ -17859,7 +18105,7 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Disrupting Shout</t>
+          <t>Challenging Shout</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
@@ -17868,15 +18114,20 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="18" t="inlineStr">
-        <is>
-          <t>Situational (no fixed key — bind where you like):</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Intervene, Wrecking Throw</t>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+Z</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Intervene</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="inlineStr">
+        <is>
+          <t>Defensive</t>
         </is>
       </c>
     </row>
@@ -18844,7 +19095,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Fel Eruption</t>
+          <t>Sigil of Chains</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
@@ -18856,46 +19107,68 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Ctrl+V</t>
+          <t>Ctrl+Z</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Imprison</t>
-        </is>
-      </c>
-      <c r="C27" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
+          <t>Fel Devastation</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>Defensive</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
+          <t>Ctrl+C</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Fel Eruption</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+V</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Imprison</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
           <t>Ctrl+F1</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>Soul Carver</t>
         </is>
       </c>
-      <c r="C28" s="15" t="inlineStr">
+      <c r="C30" s="15" t="inlineStr">
         <is>
           <t>Cooldown</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="18" t="inlineStr">
-        <is>
-          <t>Situational (no fixed key — bind where you like):</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Fel Devastation, Sigil of Chains</t>
         </is>
       </c>
     </row>
@@ -18910,7 +19183,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -19346,29 +19619,63 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
+          <t>Ctrl+Q</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Dash</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+F</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Prowl</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
           <t>Ctrl+V</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>Remove Corruption</t>
         </is>
       </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="C28" s="13" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="18" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="18" t="inlineStr">
         <is>
           <t>Situational (no fixed key — bind where you like):</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Bear Form, Dash, Prowl</t>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Bear Form</t>
         </is>
       </c>
     </row>
@@ -19378,530 +19685,6 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>Key</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>Ability</t>
-        </is>
-      </c>
-      <c r="C1" s="5" t="inlineStr">
-        <is>
-          <t>Role</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>Skull Bash</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>Interrupt</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>Q</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>Wild Charge</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>Movement</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Shred</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>Rotation</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Rake</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>Rotation</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Thrash</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>Rotation</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>Rip</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>Spender</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Ferocious Bite</t>
-        </is>
-      </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>Spender</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Rebirth</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>Utility</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Travel Form</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>Mobility</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Incapacitating Roar</t>
-        </is>
-      </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Barkskin</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>Defensive</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Survival Instincts</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="inlineStr">
-        <is>
-          <t>Defensive (major)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Maim</t>
-        </is>
-      </c>
-      <c r="C14" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>F1</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Berserk</t>
-        </is>
-      </c>
-      <c r="C15" s="15" t="inlineStr">
-        <is>
-          <t>Big cooldown</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>F2</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Renewal</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>Self-heal</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>F3</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Incarnation: Avatar of Ashamane</t>
-        </is>
-      </c>
-      <c r="C17" s="15" t="inlineStr">
-        <is>
-          <t>Cooldown</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>F4</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Recuperate</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>Sustain / HoT</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>Shift+Q</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Stampeding Roar</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>Movement</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>Shift+1</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Swipe</t>
-        </is>
-      </c>
-      <c r="C20" s="10" t="inlineStr">
-        <is>
-          <t>Rotation</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>Shift+4</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Primal Wrath</t>
-        </is>
-      </c>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>Spender</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>Shift+F</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Prowl</t>
-        </is>
-      </c>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>Utility</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>Shift+R</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Cat Form</t>
-        </is>
-      </c>
-      <c r="C23" s="12" t="inlineStr">
-        <is>
-          <t>Utility</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>Shift+X</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Moonkin Form</t>
-        </is>
-      </c>
-      <c r="C24" s="12" t="inlineStr">
-        <is>
-          <t>Utility</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>Shift+C</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Entangling Roots</t>
-        </is>
-      </c>
-      <c r="C25" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>Shift+V</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Cyclone</t>
-        </is>
-      </c>
-      <c r="C26" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>Shift+F1</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>Tiger's Fury</t>
-        </is>
-      </c>
-      <c r="C27" s="15" t="inlineStr">
-        <is>
-          <t>Cooldown</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Shift+F2</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>Frenzied Regeneration</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>Self-heal</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>Ctrl+V</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>Remove Corruption</t>
-        </is>
-      </c>
-      <c r="C29" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="18" t="inlineStr">
-        <is>
-          <t>Situational (no fixed key — bind where you like):</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Bear Form, Dash, Soothe</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -19974,7 +19757,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Mangle</t>
+          <t>Shred</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
@@ -19991,7 +19774,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Thrash</t>
+          <t>Rake</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
@@ -20008,7 +19791,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Moonfire</t>
+          <t>Thrash</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
@@ -20025,7 +19808,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Maul</t>
+          <t>Rip</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
@@ -20037,250 +19820,250 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Rebirth</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>Utility</t>
+          <t>Ferocious Bite</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>Spender</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Travel Form</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>Mobility</t>
+          <t>Rebirth</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>R</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Ironfur</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>Defensive</t>
+          <t>Travel Form</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Mobility</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>X</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Barkskin</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>Defensive</t>
+          <t>Incapacitating Roar</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Survival Instincts</t>
+          <t>Barkskin</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>Defensive (major)</t>
+          <t>Defensive</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Typhoon</t>
-        </is>
-      </c>
-      <c r="C13" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
+          <t>Survival Instincts</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>Defensive (major)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Berserk</t>
-        </is>
-      </c>
-      <c r="C14" s="15" t="inlineStr">
-        <is>
-          <t>Big cooldown</t>
+          <t>Maim</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Renewal</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>Self-heal</t>
+          <t>Berserk</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>Big cooldown</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Incarnation: Guardian of Ursoc</t>
-        </is>
-      </c>
-      <c r="C16" s="15" t="inlineStr">
-        <is>
-          <t>Cooldown</t>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>Self-heal</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F3</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Recuperate</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>Sustain / HoT</t>
+          <t>Incarnation: Avatar of Ashamane</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>Cooldown</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Shift+Q</t>
+          <t>F4</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Stampeding Roar</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>Movement</t>
+          <t>Recuperate</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>Sustain / HoT</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Shift+1</t>
+          <t>Shift+Q</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Swipe</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>Rotation</t>
+          <t>Stampeding Roar</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Movement</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Shift+F</t>
+          <t>Shift+1</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Growl</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>Taunt</t>
+          <t>Swipe</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Rotation</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Shift+R</t>
+          <t>Shift+4</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Cat Form</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>Utility</t>
+          <t>Primal Wrath</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>Spender</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Shift+X</t>
+          <t>Shift+F</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Moonkin Form</t>
+          <t>Prowl</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
@@ -20292,46 +20075,46 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Shift+Z</t>
+          <t>Shift+R</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Rage of the Sleeper</t>
-        </is>
-      </c>
-      <c r="C23" s="14" t="inlineStr">
-        <is>
-          <t>Defensive</t>
+          <t>Cat Form</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Shift+C</t>
+          <t>Shift+X</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Incapacitating Roar</t>
-        </is>
-      </c>
-      <c r="C24" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
+          <t>Moonkin Form</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Shift+V</t>
+          <t>Shift+C</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Mighty Bash</t>
+          <t>Entangling Roots</t>
         </is>
       </c>
       <c r="C25" s="13" t="inlineStr">
@@ -20343,75 +20126,75 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Shift+F2</t>
+          <t>Shift+V</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Frenzied Regeneration</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>Self-heal</t>
+          <t>Cyclone</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Ctrl+F</t>
+          <t>Shift+F1</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Prowl</t>
-        </is>
-      </c>
-      <c r="C27" s="12" t="inlineStr">
-        <is>
-          <t>Utility</t>
+          <t>Tiger's Fury</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>Cooldown</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Ctrl+X</t>
+          <t>Shift+F2</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Soothe</t>
-        </is>
-      </c>
-      <c r="C28" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
+          <t>Frenzied Regeneration</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>Self-heal</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Ctrl+Z</t>
+          <t>Ctrl+Q</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Bristling Fur</t>
-        </is>
-      </c>
-      <c r="C29" s="14" t="inlineStr">
-        <is>
-          <t>Defensive</t>
+          <t>Dash</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>Movement</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Ctrl+C</t>
+          <t>Ctrl+X</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -20433,7 +20216,7 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Entangling Roots</t>
+          <t>Soothe</t>
         </is>
       </c>
       <c r="C31" s="13" t="inlineStr">
@@ -20450,7 +20233,582 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Bear Form, Cyclone, Dash</t>
+          <t>Bear Form</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Ability</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>Skull Bash</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>Interrupt</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Wild Charge</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Mangle</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Rotation</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Thrash</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Rotation</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Moonfire</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Rotation</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Maul</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>Spender</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Rebirth</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Travel Form</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Mobility</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Ironfur</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>Defensive</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Barkskin</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>Defensive</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Survival Instincts</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>Defensive (major)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Typhoon</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Berserk</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Big cooldown</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>Self-heal</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Incarnation: Guardian of Ursoc</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>Cooldown</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Recuperate</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>Sustain / HoT</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Shift+Q</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Stampeding Roar</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Shift+1</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Swipe</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>Rotation</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Shift+F</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Growl</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>Taunt</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Shift+R</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Cat Form</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Shift+X</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Moonkin Form</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Shift+Z</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Rage of the Sleeper</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>Defensive</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Shift+C</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Incapacitating Roar</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Shift+V</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Mighty Bash</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Shift+F2</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Frenzied Regeneration</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="inlineStr">
+        <is>
+          <t>Self-heal</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+Q</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Dash</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>Movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+F</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Prowl</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+X</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Entangling Roots</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+Z</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Bristling Fur</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>Defensive</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+C</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Soothe</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+V</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Cyclone</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="18" t="inlineStr">
+        <is>
+          <t>Situational (no fixed key — bind where you like):</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Bear Form</t>
         </is>
       </c>
     </row>

--- a/tools/keybind_sheet/MidnightHelper_Keybinds.xlsx
+++ b/tools/keybind_sheet/MidnightHelper_Keybinds.xlsx
@@ -852,7 +852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1339,39 +1339,73 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
+          <t>Ctrl+R</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Mark of the Wild</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+X</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Ursol's Vortex</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
           <t>Ctrl+V</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>Soothe</t>
         </is>
       </c>
-      <c r="C29" s="13" t="inlineStr">
+      <c r="C31" s="13" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="18" t="inlineStr">
-        <is>
-          <t>Situational (no fixed key — bind where you like):</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Bear Form</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="18" t="inlineStr">
         <is>
+          <t>Situational (no fixed key — bind where you like):</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Bear Form</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="18" t="inlineStr">
+        <is>
           <t>Click-cast / mouseover (raid frames, not keys):</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Cenarion Ward, Lifebloom, Regrowth, Rejuvenation, Swiftmend</t>
         </is>
@@ -19183,7 +19217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -19653,27 +19687,61 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
+          <t>Ctrl+R</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Mark of the Wild</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+X</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Ursol's Vortex</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
           <t>Ctrl+V</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>Remove Corruption</t>
         </is>
       </c>
-      <c r="C28" s="13" t="inlineStr">
+      <c r="C30" s="13" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="18" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="18" t="inlineStr">
         <is>
           <t>Situational (no fixed key — bind where you like):</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Bear Form</t>
         </is>
@@ -19690,7 +19758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20194,44 +20262,95 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Ctrl+X</t>
+          <t>Ctrl+F</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Remove Corruption</t>
-        </is>
-      </c>
-      <c r="C30" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
+          <t>Mark of the Wild</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
+          <t>Ctrl+R</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Revive</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+X</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Remove Corruption</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+C</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Ursol's Vortex</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
           <t>Ctrl+V</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>Soothe</t>
         </is>
       </c>
-      <c r="C31" s="13" t="inlineStr">
+      <c r="C34" s="13" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="18" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="18" t="inlineStr">
         <is>
           <t>Situational (no fixed key — bind where you like):</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>Bear Form</t>
         </is>
@@ -20248,7 +20367,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20519,7 +20638,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Incarnation: Guardian of Ursoc</t>
+          <t>Lunar Beam</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
@@ -20684,129 +20803,180 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Shift+F2</t>
+          <t>Shift+F1</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Frenzied Regeneration</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>Self-heal</t>
+          <t>Incarnation: Guardian of Ursoc</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>Cooldown</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Ctrl+Q</t>
+          <t>Shift+F2</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Dash</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>Movement</t>
+          <t>Frenzied Regeneration</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>Self-heal</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Ctrl+F</t>
+          <t>Shift+F3</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Prowl</t>
-        </is>
-      </c>
-      <c r="C28" s="12" t="inlineStr">
-        <is>
-          <t>Utility</t>
+          <t>Heart of the Wild</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="inlineStr">
+        <is>
+          <t>Cooldown</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Ctrl+X</t>
+          <t>Ctrl+Q</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Entangling Roots</t>
-        </is>
-      </c>
-      <c r="C29" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
+          <t>Dash</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>Movement</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Ctrl+Z</t>
+          <t>Ctrl+F</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Bristling Fur</t>
-        </is>
-      </c>
-      <c r="C30" s="14" t="inlineStr">
-        <is>
-          <t>Defensive</t>
+          <t>Prowl</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Ctrl+C</t>
+          <t>Ctrl+R</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Soothe</t>
-        </is>
-      </c>
-      <c r="C31" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
+          <t>Mark of the Wild</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
+          <t>Ctrl+X</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Entangling Roots</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+Z</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Bristling Fur</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="inlineStr">
+        <is>
+          <t>Defensive</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+C</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Soothe</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
           <t>Ctrl+V</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>Cyclone</t>
         </is>
       </c>
-      <c r="C32" s="13" t="inlineStr">
+      <c r="C35" s="13" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="18" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="18" t="inlineStr">
         <is>
           <t>Situational (no fixed key — bind where you like):</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>Bear Form</t>
         </is>

--- a/tools/keybind_sheet/MidnightHelper_Keybinds.xlsx
+++ b/tools/keybind_sheet/MidnightHelper_Keybinds.xlsx
@@ -10840,7 +10840,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Void Eruption</t>
+          <t>Voidform</t>
         </is>
       </c>
       <c r="C15" s="15" t="inlineStr">

--- a/tools/keybind_sheet/MidnightHelper_Keybinds.xlsx
+++ b/tools/keybind_sheet/MidnightHelper_Keybinds.xlsx
@@ -9679,7 +9679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10030,12 +10030,12 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Shift+V</t>
+          <t>Shift+C</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Purify</t>
+          <t>Dispel Magic</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr">
@@ -10047,73 +10047,124 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Shift+F1</t>
+          <t>Shift+V</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Power Infusion</t>
-        </is>
-      </c>
-      <c r="C22" s="15" t="inlineStr">
-        <is>
-          <t>Big cooldown</t>
+          <t>Purify</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Shift+F2</t>
+          <t>Shift+F1</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Spirit Shell</t>
+          <t>Power Infusion</t>
         </is>
       </c>
       <c r="C23" s="15" t="inlineStr">
         <is>
-          <t>Cooldown</t>
+          <t>Big cooldown</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
+          <t>Shift+F2</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Spirit Shell</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>Cooldown</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
           <t>Shift+F3</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>Rapture</t>
         </is>
       </c>
-      <c r="C24" s="15" t="inlineStr">
+      <c r="C25" s="15" t="inlineStr">
         <is>
           <t>Cooldown</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+F</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Power Word: Fortitude</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+V</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Shackle Horror</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="18" t="inlineStr">
         <is>
           <t>Situational (no fixed key — bind where you like):</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Evangelism</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="18" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="18" t="inlineStr">
         <is>
           <t>Click-cast / mouseover (raid frames, not keys):</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Flash Heal, Renew, Shadow Mend</t>
         </is>
@@ -10130,7 +10181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10469,24 +10520,24 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Power Word: Life</t>
-        </is>
-      </c>
-      <c r="C20" s="12" t="inlineStr">
-        <is>
-          <t>Utility</t>
+          <t>Dispel Magic</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Shift+V</t>
+          <t>Shift+C</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Mass Dispel</t>
+          <t>Shackle Horror</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr">
@@ -10498,46 +10549,46 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Shift+F1</t>
+          <t>Shift+V</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Power Infusion</t>
-        </is>
-      </c>
-      <c r="C22" s="15" t="inlineStr">
-        <is>
-          <t>Big cooldown</t>
+          <t>Mass Dispel</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Shift+F2</t>
+          <t>Shift+F1</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Symbol of Hope</t>
+          <t>Power Infusion</t>
         </is>
       </c>
       <c r="C23" s="15" t="inlineStr">
         <is>
-          <t>Cooldown</t>
+          <t>Big cooldown</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Shift+F3</t>
+          <t>Shift+F2</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Holy Word: Salvation</t>
+          <t>Symbol of Hope</t>
         </is>
       </c>
       <c r="C24" s="15" t="inlineStr">
@@ -10549,27 +10600,78 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
+          <t>Shift+F3</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Holy Word: Salvation</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>Cooldown</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
           <t>Ctrl+F</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Power Word: Life</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+R</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>Levitate</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
+      <c r="C27" s="12" t="inlineStr">
         <is>
           <t>Utility</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="18" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+X</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Power Word: Fortitude</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="18" t="inlineStr">
         <is>
           <t>Click-cast / mouseover (raid frames, not keys):</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Flash Heal, Heal, Holy Word: Serenity, Prayer of Mending, Renew, Shadow Mend</t>
         </is>
@@ -10586,7 +10688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10772,7 +10874,7 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Mass Dispel</t>
+          <t>Purify Disease</t>
         </is>
       </c>
       <c r="C11" s="13" t="inlineStr">
@@ -10920,12 +11022,12 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Shift+3</t>
+          <t>Shift+2</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Void Volley</t>
+          <t>Tentacle Slam</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
@@ -10937,29 +11039,29 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Shift+F</t>
+          <t>Shift+3</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Leap of Faith</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>Utility</t>
+          <t>Void Volley</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>Rotation</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Shift+R</t>
+          <t>Shift+F</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Levitate</t>
+          <t>Leap of Faith</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
@@ -10971,49 +11073,168 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Shift+F1</t>
+          <t>Shift+R</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Power Infusion</t>
-        </is>
-      </c>
-      <c r="C23" s="15" t="inlineStr">
-        <is>
-          <t>Big cooldown</t>
+          <t>Levitate</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Shift+F2</t>
+          <t>Shift+X</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Void Torrent</t>
-        </is>
-      </c>
-      <c r="C24" s="15" t="inlineStr">
-        <is>
-          <t>Cooldown</t>
+          <t>Dispel Magic</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
+          <t>Shift+C</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Shackle Horror</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Shift+V</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Mass Dispel</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Shift+F1</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Power Infusion</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>Big cooldown</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Shift+F2</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Void Torrent</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="inlineStr">
+        <is>
+          <t>Cooldown</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
           <t>Shift+F3</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>Mindbender</t>
         </is>
       </c>
-      <c r="C25" s="15" t="inlineStr">
+      <c r="C29" s="15" t="inlineStr">
+        <is>
+          <t>Cooldown</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+F</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Power Word: Fortitude</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+R</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Shadowform</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+F1</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Vampiric Embrace</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="inlineStr">
         <is>
           <t>Cooldown</t>
         </is>

--- a/tools/keybind_sheet/MidnightHelper_Keybinds.xlsx
+++ b/tools/keybind_sheet/MidnightHelper_Keybinds.xlsx
@@ -3173,7 +3173,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Multi-Shot</t>
+          <t>Wild Thrash</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">

--- a/tools/keybind_sheet/MidnightHelper_Keybinds.xlsx
+++ b/tools/keybind_sheet/MidnightHelper_Keybinds.xlsx
@@ -8587,7 +8587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Redemption</t>
+          <t>Rite of Sanctification</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Intercession</t>
+          <t>Redemption</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
@@ -8938,46 +8938,46 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Shift+X</t>
+          <t>Shift+R</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Hammer of Justice</t>
-        </is>
-      </c>
-      <c r="C21" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
+          <t>Intercession</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Shift+Z</t>
+          <t>Shift+X</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Ardent Defender</t>
-        </is>
-      </c>
-      <c r="C22" s="14" t="inlineStr">
-        <is>
-          <t>Defensive</t>
+          <t>Hammer of Justice</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Shift+C</t>
+          <t>Shift+Z</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Divine Protection</t>
+          <t>Ardent Defender</t>
         </is>
       </c>
       <c r="C23" s="14" t="inlineStr">
@@ -8989,46 +8989,46 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Shift+V</t>
+          <t>Shift+C</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Cleanse Toxins</t>
-        </is>
-      </c>
-      <c r="C24" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
+          <t>Divine Protection</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="inlineStr">
+        <is>
+          <t>Defensive</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Shift+F1</t>
+          <t>Shift+V</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Divine Toll</t>
-        </is>
-      </c>
-      <c r="C25" s="15" t="inlineStr">
-        <is>
-          <t>Cooldown</t>
+          <t>Cleanse Toxins</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Shift+F2</t>
+          <t>Shift+F1</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Sentinel</t>
+          <t>Divine Toll</t>
         </is>
       </c>
       <c r="C26" s="15" t="inlineStr">
@@ -9040,12 +9040,12 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Shift+F3</t>
+          <t>Shift+F2</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Bastion of Light</t>
+          <t>Sentinel</t>
         </is>
       </c>
       <c r="C27" s="15" t="inlineStr">
@@ -9057,29 +9057,29 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Ctrl+X</t>
+          <t>Shift+F3</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Repentance</t>
-        </is>
-      </c>
-      <c r="C28" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
+          <t>Bastion of Light</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="inlineStr">
+        <is>
+          <t>Cooldown</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Ctrl+Z</t>
+          <t>Ctrl+X</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Blessing of Protection</t>
+          <t>Blessing of Sacrifice</t>
         </is>
       </c>
       <c r="C29" s="14" t="inlineStr">
@@ -9091,12 +9091,12 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Ctrl+C</t>
+          <t>Ctrl+Z</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Blessing of Sacrifice</t>
+          <t>Blessing of Protection</t>
         </is>
       </c>
       <c r="C30" s="14" t="inlineStr">
@@ -9108,15 +9108,32 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
+          <t>Ctrl+C</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Holy Bulwark</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>Defensive</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
           <t>Ctrl+V</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>Blinding Light</t>
         </is>
       </c>
-      <c r="C31" s="13" t="inlineStr">
+      <c r="C32" s="13" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
@@ -9133,7 +9150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9285,12 +9302,12 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Redemption</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>Utility</t>
+          <t>Hand of Reckoning</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>Taunt</t>
         </is>
       </c>
     </row>
@@ -9302,7 +9319,7 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Intercession</t>
+          <t>Redemption</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
@@ -9484,29 +9501,29 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Shift+X</t>
+          <t>Shift+F</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Blessing of Protection</t>
-        </is>
-      </c>
-      <c r="C21" s="14" t="inlineStr">
-        <is>
-          <t>Defensive</t>
+          <t>Intercession</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Shift+Z</t>
+          <t>Shift+X</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Divine Protection</t>
+          <t>Blessing of Protection</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
@@ -9518,63 +9535,63 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Shift+C</t>
+          <t>Shift+Z</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Shield of Vengeance</t>
+          <t>Divine Protection</t>
         </is>
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>Defensive (major)</t>
+          <t>Defensive</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Shift+V</t>
+          <t>Shift+C</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Hammer of Justice</t>
-        </is>
-      </c>
-      <c r="C24" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
+          <t>Shield of Vengeance</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="inlineStr">
+        <is>
+          <t>Defensive (major)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Shift+F1</t>
+          <t>Shift+V</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Wake of Ashes</t>
-        </is>
-      </c>
-      <c r="C25" s="15" t="inlineStr">
-        <is>
-          <t>Cooldown</t>
+          <t>Hammer of Justice</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Shift+F2</t>
+          <t>Shift+F1</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Sentinel</t>
+          <t>Wake of Ashes</t>
         </is>
       </c>
       <c r="C26" s="15" t="inlineStr">
@@ -9586,12 +9603,12 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Shift+F3</t>
+          <t>Shift+F2</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Divine Toll</t>
+          <t>Sentinel</t>
         </is>
       </c>
       <c r="C27" s="15" t="inlineStr">
@@ -9603,46 +9620,46 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Ctrl+X</t>
+          <t>Shift+F3</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Repentance</t>
-        </is>
-      </c>
-      <c r="C28" s="13" t="inlineStr">
-        <is>
-          <t>Dispel / CC</t>
+          <t>Divine Toll</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="inlineStr">
+        <is>
+          <t>Cooldown</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Ctrl+Z</t>
+          <t>Ctrl+X</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Blessing of Sacrifice</t>
-        </is>
-      </c>
-      <c r="C29" s="14" t="inlineStr">
-        <is>
-          <t>Defensive</t>
+          <t>Repentance</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>Dispel / CC</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Ctrl+C</t>
+          <t>Ctrl+Z</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Blessing of Spellwarding</t>
+          <t>Blessing of Sacrifice</t>
         </is>
       </c>
       <c r="C30" s="14" t="inlineStr">
@@ -9654,15 +9671,32 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
+          <t>Ctrl+C</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Blessing of Spellwarding</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>Defensive</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
           <t>Ctrl+V</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>Blinding Light</t>
         </is>
       </c>
-      <c r="C31" s="13" t="inlineStr">
+      <c r="C32" s="13" t="inlineStr">
         <is>
           <t>Dispel / CC</t>
         </is>
